--- a/tame_output/ON/bt/strategyON_20231104.xlsx
+++ b/tame_output/ON/bt/strategyON_20231104.xlsx
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>19.6%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,12 +929,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.7%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.0%</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1770"/>
+  <dimension ref="A1:G1771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.066955604001347</v>
+        <v>3.06824651857159</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42236,6 +42236,29 @@
       </c>
       <c r="G1770" t="n">
         <v>4.352934888120401</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" s="2" t="n">
+        <v>45233</v>
+      </c>
+      <c r="B1771" t="n">
+        <v>3.068083032765877</v>
+      </c>
+      <c r="C1771" t="n">
+        <v>3.051179068073428</v>
+      </c>
+      <c r="D1771" t="n">
+        <v>1.550071206483375</v>
+      </c>
+      <c r="E1771" t="n">
+        <v>3.670851126353031</v>
+      </c>
+      <c r="F1771" t="n">
+        <v>2.172821969478192</v>
+      </c>
+      <c r="G1771" t="n">
+        <v>4.354872249760345</v>
       </c>
     </row>
   </sheetData>
